--- a/business_forms/046_project_manager_registration_form--business_forms.xlsx
+++ b/business_forms/046_project_manager_registration_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -788,8 +788,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -817,12 +817,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'jane_smith'}</t>
+          <t>jane_smith</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Smith'}</t>
+          <t>Jane Smith</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'joe'}</t>
+          <t>joe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Joe'}</t>
+          <t>Joe</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
